--- a/docs/design-docs/06_画面設計書_組織・カレンダー・保守部品.xlsx
+++ b/docs/design-docs/06_画面設計書_組織・カレンダー・保守部品.xlsx
@@ -18,7 +18,431 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>画面設計書 — 部署マスタ一覧</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+  </si>
+  <si>
+    <t>組織管理</t>
+  </si>
+  <si>
+    <t>画面ID</t>
+  </si>
+  <si>
+    <t>SCR-ORG-DEPT-001</t>
+  </si>
+  <si>
+    <t>画面名</t>
+  </si>
+  <si>
+    <t>部署マスタ一覧</t>
+  </si>
+  <si>
+    <t>プログラムID</t>
+  </si>
+  <si>
+    <t>PG-ORG-DEPT-001</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-ORG-DEPT-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>画面レイアウト</t>
+  </si>
+  <si>
+    <t>4階層tree表示(本社→支社→営業所→出張所)。table形式、indentで階層表現。編集/子部署追加link。統廃合履歴。</t>
+  </si>
+  <si>
+    <t>画面要素一覧</t>
+  </si>
+  <si>
+    <t>要素ID</t>
+  </si>
+  <si>
+    <t>種別</t>
+  </si>
+  <si>
+    <t>表示名</t>
+  </si>
+  <si>
+    <t>入力値/選択肢</t>
+  </si>
+  <si>
+    <t>説明</t>
+  </si>
+  <si>
+    <t>テスト難点タグ</t>
+  </si>
+  <si>
+    <t>Struts1マッピング</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>Action Path</t>
+  </si>
+  <si>
+    <t>/org/dept/list</t>
+  </si>
+  <si>
+    <t>Action Class</t>
+  </si>
+  <si>
+    <t>部署マスタListAction</t>
+  </si>
+  <si>
+    <t>Form Bean</t>
+  </si>
+  <si>
+    <t>部署マスタSearchForm</t>
+  </si>
+  <si>
+    <t>テスト難点詳細</t>
+  </si>
+  <si>
+    <t>4階層tree indent検証</t>
+  </si>
+  <si>
+    <t>階層別追加/編集画面遷移</t>
+  </si>
+  <si>
+    <t>画面設計書 — 部署マスタ登録編集</t>
+  </si>
+  <si>
+    <t>SCR-ORG-DEPT-002</t>
+  </si>
+  <si>
+    <t>部署マスタ登録編集</t>
+  </si>
+  <si>
+    <t>PG-ORG-DEPT-002</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-ORG-DEPT-002</t>
+  </si>
+  <si>
+    <t>上位部署選択(tree Popup→値反映)。有効期間(開始/終了)。過去日異動警告。部署種別select。</t>
+  </si>
+  <si>
+    <t>/org/dept/save</t>
+  </si>
+  <si>
+    <t>部署マスタSaveAction</t>
+  </si>
+  <si>
+    <t>部署マスタForm</t>
+  </si>
+  <si>
+    <t>過去日異動警告validation</t>
+  </si>
+  <si>
+    <t>tree Popup選択値反映</t>
+  </si>
+  <si>
+    <t>画面設計書 — 担当者マスタ一覧</t>
+  </si>
+  <si>
+    <t>SCR-ORG-EMP-001</t>
+  </si>
+  <si>
+    <t>担当者マスタ一覧</t>
+  </si>
+  <si>
+    <t>PG-ORG-EMP-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-ORG-EMP-001</t>
+  </si>
+  <si>
+    <t>複合検索(部署×職位×資格checkbox×入社年)。一覧：社員番号/氏名/部署/職位/資格/認定期限。期限切赤背景。一括lock/解除。</t>
+  </si>
+  <si>
+    <t>/org/emp/list</t>
+  </si>
+  <si>
+    <t>担当者マスタListAction</t>
+  </si>
+  <si>
+    <t>担当者マスタSearchForm</t>
+  </si>
+  <si>
+    <t>複数checkbox資格選択AND/OR検索</t>
+  </si>
+  <si>
+    <t>期限切CSS class検証</t>
+  </si>
+  <si>
+    <t>画面設計書 — 担当者マスタ登録編集</t>
+  </si>
+  <si>
+    <t>SCR-ORG-EMP-002</t>
+  </si>
+  <si>
+    <t>担当者マスタ登録編集</t>
+  </si>
+  <si>
+    <t>PG-ORG-EMP-002</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-ORG-EMP-002</t>
+  </si>
+  <si>
+    <t>5section大form：①基本情報②所属職位③保有資格(資格毎認定日/期限)④点検員認定⑤account。password確認一致。loginID重複check。</t>
+  </si>
+  <si>
+    <t>/org/emp/save</t>
+  </si>
+  <si>
+    <t>担当者マスタSaveAction</t>
+  </si>
+  <si>
+    <t>担当者マスタForm</t>
+  </si>
+  <si>
+    <t>5section一括validation</t>
+  </si>
+  <si>
+    <t>資格毎期限validation(n個条件付)</t>
+  </si>
+  <si>
+    <t>password一致</t>
+  </si>
+  <si>
+    <t>loginID重複</t>
+  </si>
+  <si>
+    <t>画面設計書 — 休日カレンダー一覧</t>
+  </si>
+  <si>
+    <t>カレンダー管理</t>
+  </si>
+  <si>
+    <t>SCR-CAL-LIST-001</t>
+  </si>
+  <si>
+    <t>休日カレンダー一覧</t>
+  </si>
+  <si>
+    <t>PG-CAL-LIST-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-CAL-LIST-001</t>
+  </si>
+  <si>
+    <t>年度選択→月別calendar表示(table 7列×5-6行)。休日種別色分け(法定=赤/会社指定=青/点検停止=黄)。日付click→登録編集。</t>
+  </si>
+  <si>
+    <t>/cal/list/list</t>
+  </si>
+  <si>
+    <t>休日カレンダーListAction</t>
+  </si>
+  <si>
+    <t>休日カレンダーSearchForm</t>
+  </si>
+  <si>
+    <t>月別calendar cell色検証</t>
+  </si>
+  <si>
+    <t>年度切替data範囲</t>
+  </si>
+  <si>
+    <t>画面設計書 — 休日登録編集</t>
+  </si>
+  <si>
+    <t>SCR-CAL-REG-001</t>
+  </si>
+  <si>
+    <t>休日登録編集</t>
+  </si>
+  <si>
+    <t>PG-CAL-REG-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-CAL-REG-001</t>
+  </si>
+  <si>
+    <t>日付範囲指定(from/to)→一括登録。重複check。振替出勤日設定。休日種別選択。</t>
+  </si>
+  <si>
+    <t>/cal/reg/save</t>
+  </si>
+  <si>
+    <t>休日SaveAction</t>
+  </si>
+  <si>
+    <t>休日Form</t>
+  </si>
+  <si>
+    <t>範囲指定一括登録重複check</t>
+  </si>
+  <si>
+    <t>計画停止期間と通常休日重複</t>
+  </si>
+  <si>
+    <t>画面設計書 — 保守部品一覧</t>
+  </si>
+  <si>
+    <t>保守部品管理</t>
+  </si>
+  <si>
+    <t>SCR-PRT-LIST-001</t>
+  </si>
+  <si>
+    <t>保守部品一覧</t>
+  </si>
+  <si>
+    <t>PG-PRT-LIST-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-PRT-LIST-001</t>
+  </si>
+  <si>
+    <t>複合検索(設備種別×部品種別×在庫status×keyword)。在庫badge(充足=緑/僅少=黄/在庫切=赤)。</t>
+  </si>
+  <si>
+    <t>/prt/list/list</t>
+  </si>
+  <si>
+    <t>保守部品ListAction</t>
+  </si>
+  <si>
+    <t>保守部品SearchForm</t>
+  </si>
+  <si>
+    <t>在庫badge色分け(CSS class)</t>
+  </si>
+  <si>
+    <t>在庫僅少/切れ境界値</t>
+  </si>
+  <si>
+    <t>画面設計書 — 保守部品登録編集</t>
+  </si>
+  <si>
+    <t>SCR-PRT-REG-001</t>
+  </si>
+  <si>
+    <t>保守部品登録編集</t>
+  </si>
+  <si>
+    <t>PG-PRT-REG-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-PRT-REG-001</t>
+  </si>
+  <si>
+    <t>適用設備選択(checkbox tree：設備種別→設備名2階層 複数選択可)。発注点/安全在庫数(発注点&amp;gt;安全在庫validation)。添付file(仕様書PDF)。</t>
+  </si>
+  <si>
+    <t>/prt/reg/save</t>
+  </si>
+  <si>
+    <t>保守部品SaveAction</t>
+  </si>
+  <si>
+    <t>保守部品Form</t>
+  </si>
+  <si>
+    <t>checkbox tree階層表示</t>
+  </si>
+  <si>
+    <t>発注点&amp;gt;安全在庫validation</t>
+  </si>
+  <si>
+    <t>画面設計書 — 部品使用実績一覧</t>
+  </si>
+  <si>
+    <t>SCR-PRT-USAGE-001</t>
+  </si>
+  <si>
+    <t>部品使用実績一覧</t>
+  </si>
+  <si>
+    <t>PG-PRT-USAGE-001</t>
+  </si>
+  <si>
+    <t>DOC-SCR-SCR-PRT-USAGE-001</t>
+  </si>
+  <si>
+    <t>期間×設備種別×部品検索。一覧：使用日/部品名/設備名/使用量/使用前後在庫/目的。在庫発注点下回→警告。</t>
+  </si>
+  <si>
+    <t>/prt/usage/list</t>
+  </si>
+  <si>
+    <t>部品使用実績ListAction</t>
+  </si>
+  <si>
+    <t>部品使用実績SearchForm</t>
+  </si>
+  <si>
+    <t>在庫自動引当表示(使用後在庫≦発注点で警告)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
